--- a/review/abilities/workbooks/20_Class_Arcanist.xlsx
+++ b/review/abilities/workbooks/20_Class_Arcanist.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -25,11 +25,11 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Level 7'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'All Signatures'!$A$4:$M$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -197,7 +197,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -234,19 +234,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -889,7 +876,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Cast and Scatter; Leave a Window; Arcane Deflection</t>
+          <t>Siphon Cast; Create a Window; Arcane Deflection</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -909,7 +896,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Fold the Distance; Choose the Edge; Open the Circle</t>
+          <t>Folded Aegis; Choose the Edge; Open the Circle</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
@@ -1214,27 +1201,27 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Your single-target spell; choose one visible adjacent unoccupied origin square before rolling.</t>
+          <t>One of your spell attacks; choose one visible, unoccupied square within 6 squares of you before rolling.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Your single-target spell may originate from the chosen square. Determine cover and attack path from there, but measure range from you. You must still see the target and cannot cast through an opaque barrier. This changes only the spell’s origin; it adds no roll or action.</t>
+          <t>Choose one of your spell attacks. It can originate from any visible, unoccupied square within 6 squares of you. Determine cover and attack path from that square, but measure range from you. You must know the target’s location. Roll the spell attack normally.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Your single-target spell may originate from the chosen square. Determine cover and attack path from there, but measure range from you. You must still see the target and cannot cast through an opaque barrier. This changes only the spell’s origin; it adds no roll or action.</t>
+          <t>Choose one of your spell attacks. It can originate from any visible, unoccupied square within 6 squares of you. Determine cover and attack path from that square, but measure range from you. You must know the target’s location. Roll the spell attack normally.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Elegant spatial tool: the spell originates from an adjacent square while range stays measured from you. Rewards positioning and cover play without adding a roll.</t>
+          <t>Six-square visible origin for spell attacks: cover and path come from the origin, range stays measured from the caster, and the target's location must be known. Strong tactical reach without through-wall casting.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify that the origin must be visible and that a spell cannot pass through an opaque barrier; the current text implies both but does not show an example.</t>
+          <t>Approved: spell attacks only; visible, unoccupied origin within 6 squares; know the target's location; roll the spell attack normally.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1250,7 +1237,7 @@
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="66.5" customHeight="1">
+    <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Deliberate Spark</t>
@@ -1263,7 +1250,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1273,27 +1260,27 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>One creature hit by your Main Action damaging spell.</t>
+          <t>One corner of your square; each creature in the four squares that share that corner and are in line of effect.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>On a Standard or Strong result, after resolving the spell, you may push one of its targets 1 square directly away from you. Use this once on your turn. It adds no direct damage; normal collision rules apply.</t>
+          <t>Choose a corner of your square and spark a brief flare of gas there. Each creature in the four squares that share that corner, including you, is pushed 2 squares directly away from that corner. A creature in more than one of those squares is pushed once. The spark does not provoke opportunity attacks.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>On a Standard or Strong result, after resolving the spell, you may push one of its targets 1 square directly away from you. Use this once on your turn. It adds no direct damage; normal collision rules apply.</t>
+          <t>Choose a corner of your square and spark a brief flare of gas there. Each creature in the four squares that share that corner, including you, is pushed 2 squares directly away from that corner. A creature in more than one of those squares is pushed once. The spark does not provoke opportunity attacks. Resolve the push as forced movement; normal collision rules apply.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Small push rider on a damaging spell; makes every spell feel physical without spending another action.</t>
+          <t>Active Maneuver: choose a corner of your square; creatures in the four squares sharing that corner are pushed 2 squares away from it, including you. Strong localized control and self-mobility; the spark does not provoke.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Confirm it is once on your turn and whether the pushed target must be one of the spell's targets. Add a one-line example.</t>
+          <t>Approved: Maneuver, corner 2x2 area, line of effect, 2-square forced push, spark does not provoke opportunity attacks.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1309,7 +1296,7 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="79" customHeight="1">
+    <row r="7" ht="66.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Study the Pattern</t>
@@ -1332,27 +1319,27 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One visible ongoing magical effect within 5 squares.</t>
+          <t>One ongoing magical effect within 5 squares that you are aware of.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Learn its purpose, whether it is sustained by a creature or an object, and its remaining duration if it has one. The DA also identifies one actual way to end or avoid it, if one exists. Gain 1 Boon to your next roll using that information before the scene ends.</t>
+          <t>Learn its origin and purpose, whether a creature or object sustains it, and its duration if it has one. You also become aware of how to end the effect if it is possible. Gain 1 Boon to your next roll using that information before the scene ends.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Learn its purpose, whether it is sustained by a creature or an object, and its remaining duration if it has one. The DA also identifies one actual way to end or avoid it, if one exists. Gain 1 Boon to your next roll using that information before the scene ends. This reveals no hidden caster location, grants no dispelling ability, and does not identify an item’s dormant properties or curses.</t>
+          <t>Learn its origin and purpose, whether a creature or object sustains it, and its duration if it has one. You also become aware of how to end the effect if it is possible. Gain 1 Boon to your next roll using that information before the scene ends.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Maneuver-based magical analysis with a concrete way to end or avoid the effect. Gives the Arcanist an information role in combat.</t>
+          <t>Strong information Maneuver: learn origin, purpose, sustainer, duration and how to end the effect, then gain 1 Boon using that information. No negative exclusions.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Define 'purpose' and what happens with effects that have no duration. A short example would reduce table variance.</t>
+          <t>Approved: learn origin/purpose/sustainer/duration/end condition; one Boon per effect per scene.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1385,15 +1372,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1517,7 +1501,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="79" customHeight="1">
+    <row r="5" ht="91.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Arcane Deflection</t>
@@ -1540,86 +1524,86 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Self or one willing ally within 3 squares, before its defense against a spell.</t>
+          <t>Self, before your defense against a spell. The point of impact is one corner of your square.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Grant 2 Boons to that defense, including a defense against an area spell. After a Strong defense, you may push the visible caster 1 square directly away from you if it is within 5 squares. Make no extra roll; this does not cancel the spell or protect other targets.</t>
+          <t>Roll your defense normally. You take no damage from the spell. Choose a corner of your square as the point of impact. Each creature in the four squares that share that corner, including you, is pushed a number of squares equal to the spell’s raw damage before your defense or resistance, directly away from that corner.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Grant 2 Boons to that defense, including a defense against an area spell. After a Strong defense, you may push the visible caster 1 square directly away from you if it is within 5 squares. Make no extra roll; this does not cancel the spell or protect other targets.</t>
+          <t>Roll your defense normally. You take no damage from the spell. Choose a corner of your square as the point of impact. Each creature in the four squares that share that corner, including you, is pushed a number of squares equal to the spell’s raw damage before your defense or resistance, directly away from that corner. Resolve the push as forced movement; normal collision rules apply.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Reaction granting 2 Boons to a spell defense, plus a push on a Strong defense. Strong but narrow; a clear signature upgrade over shared defense cards.</t>
+          <t>Self-only Reaction that converts a spell's raw damage into a 1:1 forced push around a chosen corner, affecting all four squares including the Arcanist. Big, risky and very spatial.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>2 Boons is above the usual 1. Keep if intentional, but playtest; clarify that the push happens after the defense and only against a visible caster.</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Approved: self only; roll defense normally; take no damage; 1 square of push per point of raw damage; four squares around the impact corner, including you.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>2 Boons</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Cast and Scatter</t>
+          <t>Create a Window</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-arcanist-cast-and-scatter</t>
+          <t>signature-arcanist-leave-a-window</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Self, after your Main Action spell resolves.</t>
+          <t>One willing ally on their turn, before they take any action; choose two visible, unoccupied squares within 6 squares of you.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Move up to 2 squares without provoking. Choose a legal route and free endpoint. This uses no movement allowance and does not change the spell’s result.</t>
+          <t>The two squares become connected windows until the end of the ally’s turn. The ally can use the windows once at any point during their turn, either to move through one and out the other, spending 1 square of movement, or to make one attack through one window, measuring range and cover from the other.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Move up to 2 squares without provoking. Choose a legal route and free endpoint. This uses no movement allowance and does not change the spell’s result.</t>
+          <t>The two squares become connected windows until the end of the ally’s turn. The ally can use the windows once at any point during their turn, either to move through one and out the other, spending 1 square of movement, or to make one attack through one window, measuring range and cover from the other. The ally must be able to see the window they use. The windows vanish at the end of the ally’s turn. This movement does not provoke opportunity attacks.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Free 2-square move after casting; strong hit-and-run identity and a clear reason to stay mobile.</t>
+          <t>Reaction portal: connect two squares so an ally can move through or attack through once during their turn. Strong positional support with a clean end-of-turn expiry.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the move happens if the spell is countered, misses or has no effect. Current wording says after it resolves.</t>
+          <t>Approved: Reaction before the ally takes any action; two visible, unoccupied squares within 6; one use either movement or attack; lasts until the end of the ally's turn.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1635,15 +1619,15 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="66.5" customHeight="1">
+    <row r="7" ht="79" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Leave a Window</t>
+          <t>Siphon Cast</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-arcanist-leave-a-window</t>
+          <t>signature-arcanist-cast-and-scatter</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1658,27 +1642,27 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One creature in your area spell, chosen before rolling.</t>
+          <t>Self, when you cast a Main Action spell that requires a roll.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Exclude the chosen creature from every effect of that spell. Determine the least favorable net Boons/Banes from the remaining targets and roll once as usual. This changes no range or area and grants no immunity to later effects from other sources.</t>
+          <t>Take 1 Bane on the spell’s roll. The spell resolves as you vanish from your original position. Choose a free square you can see within 4 squares of that position; at the start of your next turn, you rematerialize there. You are untargetable while vanished.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Exclude the chosen creature from every effect of that spell. Determine the least favorable net Boons/Banes from the remaining targets and roll once as usual. This changes no range or area and grants no immunity to later effects from other sources.</t>
+          <t>Take 1 Bane on the spell’s roll. The spell resolves as you vanish from your original position. Choose a free square you can see within 4 squares of that position; at the start of your next turn, you rematerialize there. You are untargetable while vanished. Your current turn ends, and you have no actions or reactions until you rematerialize. This movement does not provoke opportunity attacks.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Party-friendly area casting: exclude one creature before the roll. Essential for a blaster who wants allies in the fight.</t>
+          <t>Siphon Cast: pay 1 Bane, vanish as the spell resolves, and rematerialize up to 4 squares away at the start of your next turn. Untargetable while gone, but you lose the rest of your turn and your reactions.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Good as written. Confirm the excluded creature is not counted for the 'least favorable' Boons/Banes; the text says remaining targets, which is correct.</t>
+          <t>Approved: any Main Action spell that requires a roll; 1 Bane; simultaneous vanish; return at the start of your next turn; visible free destination within 4 squares.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1711,15 +1695,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1843,7 +1824,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="66.5" customHeight="1">
+    <row r="5" ht="91.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Choose the Edge</t>
@@ -1856,37 +1837,37 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Up to two creatures affected by your Standard or Strong Main Action spell.</t>
+          <t>Self, when you cast a single-target spell that requires a roll.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>After the spell resolves, push each chosen creature up to 2 squares directly away from you. Choose the order. This adds no direct damage; use normal forced movement and collisions. The spell need not already cause displacement.</t>
+          <t>You take 2 Banes on defense rolls until the start of your next turn. Choose two different targets or directions before rolling. Resolve the triggering spell twice, once for each choice, with a separate roll for each casting. Each casting uses the spell’s normal range and effects. Pay any costs for the spell once.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>After the spell resolves, push each chosen creature up to 2 squares directly away from you. Choose the order. This adds no direct damage; use normal forced movement and collisions. The spell need not already cause displacement.</t>
+          <t>You take 2 Banes on defense rolls until the start of your next turn. Choose two different targets or directions before rolling. Resolve the triggering spell twice, once for each choice, with a separate roll for each casting. Each casting uses the spell’s normal range and effects. Pay any costs for the spell once.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Pushes up to two spell targets 2 squares. Useful, but a modest effect for a Master signature slot.</t>
+          <t>Self-only Reaction that splits a single-target spell into two castings with separate rolls, at the cost of 2 Banes on defense until the next turn. Strong nova with a real defensive risk.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Consider a Master-scale rider: push 3, choose direction, or knock prone on a Strong result. Otherwise accept it as a simple option and say so in the class guidance.</t>
+          <t>Approved: single-target spell with a roll; choose two different targets or directions before rolling; separate rolls; pay the spell cost once; 2 Banes on defense until the start of the next turn.</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -1902,10 +1883,10 @@
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="91.5" customHeight="1">
+    <row r="6" ht="79" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Fold the Distance</t>
+          <t>Folded Aegis</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1915,37 +1896,37 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Self and optionally one adjacent willing ally; visible free destinations within 4 squares of you.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Teleport yourself to a chosen destination. You may bring the ally to a separate free square adjacent to your destination, also within range. Both destinations must fit their occupants; no opaque barrier may separate either traveler from its destination. Neither traveler provokes, and the ally spends no action.</t>
+          <t>For 2 hours, you are wrapped in magical heavy armor. You gain physical resistance 3, fire resistance 3 and cold resistance 3. Use the highest matching resistance for each damage type, to the normal cap of 3. The armor is weightless and needs no armor training.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Teleport yourself to a chosen destination. You may bring the ally to a separate free square adjacent to your destination, also within range. Both destinations must fit their occupants; no opaque barrier may separate either traveler from its destination. Neither traveler provokes, and the ally spends no action.</t>
+          <t>For 2 hours, you are wrapped in magical heavy armor. You gain physical resistance 3, fire resistance 3 and cold resistance 3. Use the highest matching resistance for each damage type, to the normal cap of 3. The armor is weightless and needs no armor training.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Teleport self and one adjacent ally up to 4 squares; excellent escape and repositioning.</t>
+          <t>Folded Aegis: once per day for 2 hours, wrap yourself in magical heavy armor with resistance 3 to physical, fire and cold. Strong defensive capstone.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify line of effect and whether the ally can be moved if it is immobile or Grappled. The 'no opaque barrier' clause is good.</t>
+          <t>Approved: Main Action, self, 2 hours, once per day, resistance 3 to physical, fire and cold, highest matching resistance and normal cap 3. Weightless and needs no armor training.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1961,7 +1942,7 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="91.5" customHeight="1">
+    <row r="7" ht="41.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Open the Circle</t>
@@ -1979,7 +1960,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1989,22 +1970,22 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Each recipient gains 1 Boon to defenses against spells until the start of your next turn. During that time, each recipient gains Stability 2 for the first forced movement against them, including being struck in a collision chain. Use the highest applicable Stability, maximum 3.</t>
+          <t>Each recipient gains 1 Boon to defenses against spells until the start of your next turn. During that time, each recipient gains Stability 2.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Each recipient gains 1 Boon to defenses against spells until the start of your next turn. During that time, each recipient gains Stability 2 for the first forced movement against them, including being struck in a collision chain. Use the highest applicable Stability, maximum 3. This grant expires after that forced movement even if a higher Stability applied; it never reduces distance a second time. This is a ward, not physical cover.</t>
+          <t>Each recipient gains 1 Boon to defenses against spells until the start of your next turn. During that time, each recipient gains Stability 2.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Ward for self and nearby allies: 1 Boon against spells and Stability 2 against the first forced movement. Strong protective capstone.</t>
+          <t>Ward for self and nearby allies: 1 Boon against spells and Stability 2 until the start of your next turn. Strong, simple protective capstone.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Stability grant is consumed even if a higher Stability applies (text says yes) and whether allies keep the Boon if they leave the circle.</t>
+          <t>Approved: 1 Boon against spells plus Stability 2, with no special tracking or exceptions. Reapplying replaces the previous ward.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2037,15 +2018,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2197,22 +2175,22 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Your single-target spell; choose one visible adjacent unoccupied origin square before rolling.</t>
+          <t>One of your spell attacks; choose one visible, unoccupied square within 6 squares of you before rolling.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Your single-target spell may originate from the chosen square. Determine cover and attack path from there, but measure range from you. You must still see the target and cannot cast through an opaque barrier. This changes only the spell’s origin; it adds no roll or action.</t>
+          <t>Choose one of your spell attacks. It can originate from any visible, unoccupied square within 6 squares of you. Determine cover and attack path from that square, but measure range from you. You must know the target’s location. Roll the spell attack normally.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Elegant spatial tool: the spell originates from an adjacent square while range stays measured from you. Rewards positioning and cover play without adding a roll.</t>
+          <t>Six-square visible origin for spell attacks: cover and path come from the origin, range stays measured from the caster, and the target's location must be known. Strong tactical reach without through-wall casting.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify that the origin must be visible and that a spell cannot pass through an opaque barrier; the current text implies both but does not show an example.</t>
+          <t>Approved: spell attacks only; visible, unoccupied origin within 6 squares; know the target's location; roll the spell attack normally.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -2228,7 +2206,7 @@
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="66.5" customHeight="1">
+    <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
@@ -2246,7 +2224,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -2256,22 +2234,22 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>One creature hit by your Main Action damaging spell.</t>
+          <t>One corner of your square; each creature in the four squares that share that corner and are in line of effect.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>On a Standard or Strong result, after resolving the spell, you may push one of its targets 1 square directly away from you. Use this once on your turn. It adds no direct damage; normal collision rules apply.</t>
+          <t>Choose a corner of your square and spark a brief flare of gas there. Each creature in the four squares that share that corner, including you, is pushed 2 squares directly away from that corner. A creature in more than one of those squares is pushed once. The spark does not provoke opportunity attacks.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Small push rider on a damaging spell; makes every spell feel physical without spending another action.</t>
+          <t>Active Maneuver: choose a corner of your square; creatures in the four squares sharing that corner are pushed 2 squares away from it, including you. Strong localized control and self-mobility; the spark does not provoke.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Confirm it is once on your turn and whether the pushed target must be one of the spell's targets. Add a one-line example.</t>
+          <t>Approved: Maneuver, corner 2x2 area, line of effect, 2-square forced push, spark does not provoke opportunity attacks.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -2287,7 +2265,7 @@
       <c r="L6" s="8" t="inlineStr"/>
       <c r="M6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="79" customHeight="1">
+    <row r="7" ht="66.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2315,22 +2293,22 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>One visible ongoing magical effect within 5 squares.</t>
+          <t>One ongoing magical effect within 5 squares that you are aware of.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Learn its purpose, whether it is sustained by a creature or an object, and its remaining duration if it has one. The DA also identifies one actual way to end or avoid it, if one exists. Gain 1 Boon to your next roll using that information before the scene ends.</t>
+          <t>Learn its origin and purpose, whether a creature or object sustains it, and its duration if it has one. You also become aware of how to end the effect if it is possible. Gain 1 Boon to your next roll using that information before the scene ends.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Maneuver-based magical analysis with a concrete way to end or avoid the effect. Gives the Arcanist an information role in combat.</t>
+          <t>Strong information Maneuver: learn origin, purpose, sustainer, duration and how to end the effect, then gain 1 Boon using that information. No negative exclusions.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Define 'purpose' and what happens with effects that have no duration. A short example would reduce table variance.</t>
+          <t>Approved: learn origin/purpose/sustainer/duration/end condition; one Boon per effect per scene.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2346,7 +2324,7 @@
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
-    <row r="8" ht="79" customHeight="1">
+    <row r="8" ht="91.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>3</t>
@@ -2374,38 +2352,38 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Self or one willing ally within 3 squares, before its defense against a spell.</t>
+          <t>Self, before your defense against a spell. The point of impact is one corner of your square.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Grant 2 Boons to that defense, including a defense against an area spell. After a Strong defense, you may push the visible caster 1 square directly away from you if it is within 5 squares. Make no extra roll; this does not cancel the spell or protect other targets.</t>
+          <t>Roll your defense normally. You take no damage from the spell. Choose a corner of your square as the point of impact. Each creature in the four squares that share that corner, including you, is pushed a number of squares equal to the spell’s raw damage before your defense or resistance, directly away from that corner.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Reaction granting 2 Boons to a spell defense, plus a push on a Strong defense. Strong but narrow; a clear signature upgrade over shared defense cards.</t>
+          <t>Self-only Reaction that converts a spell's raw damage into a 1:1 forced push around a chosen corner, affecting all four squares including the Arcanist. Big, risky and very spatial.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>2 Boons is above the usual 1. Keep if intentional, but playtest; clarify that the push happens after the defense and only against a visible caster.</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Approved: self only; roll defense normally; take no damage; 1 square of push per point of raw damage; four squares around the impact corner, including you.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>2 Boons</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr"/>
       <c r="M8" s="8" t="inlineStr"/>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="91.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>3</t>
@@ -2413,42 +2391,42 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cast and Scatter</t>
+          <t>Create a Window</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>signature-arcanist-cast-and-scatter</t>
+          <t>signature-arcanist-leave-a-window</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Self, after your Main Action spell resolves.</t>
+          <t>One willing ally on their turn, before they take any action; choose two visible, unoccupied squares within 6 squares of you.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Move up to 2 squares without provoking. Choose a legal route and free endpoint. This uses no movement allowance and does not change the spell’s result.</t>
+          <t>The two squares become connected windows until the end of the ally’s turn. The ally can use the windows once at any point during their turn, either to move through one and out the other, spending 1 square of movement, or to make one attack through one window, measuring range and cover from the other.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Free 2-square move after casting; strong hit-and-run identity and a clear reason to stay mobile.</t>
+          <t>Reaction portal: connect two squares so an ally can move through or attack through once during their turn. Strong positional support with a clean end-of-turn expiry.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the move happens if the spell is countered, misses or has no effect. Current wording says after it resolves.</t>
+          <t>Approved: Reaction before the ally takes any action; two visible, unoccupied squares within 6; one use either movement or attack; lasts until the end of the ally's turn.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -2464,7 +2442,7 @@
       <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="66.5" customHeight="1">
+    <row r="10" ht="79" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>3</t>
@@ -2472,12 +2450,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Leave a Window</t>
+          <t>Siphon Cast</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>signature-arcanist-leave-a-window</t>
+          <t>signature-arcanist-cast-and-scatter</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -2492,22 +2470,22 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>One creature in your area spell, chosen before rolling.</t>
+          <t>Self, when you cast a Main Action spell that requires a roll.</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Exclude the chosen creature from every effect of that spell. Determine the least favorable net Boons/Banes from the remaining targets and roll once as usual. This changes no range or area and grants no immunity to later effects from other sources.</t>
+          <t>Take 1 Bane on the spell’s roll. The spell resolves as you vanish from your original position. Choose a free square you can see within 4 squares of that position; at the start of your next turn, you rematerialize there. You are untargetable while vanished.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Party-friendly area casting: exclude one creature before the roll. Essential for a blaster who wants allies in the fight.</t>
+          <t>Siphon Cast: pay 1 Bane, vanish as the spell resolves, and rematerialize up to 4 squares away at the start of your next turn. Untargetable while gone, but you lose the rest of your turn and your reactions.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Good as written. Confirm the excluded creature is not counted for the 'least favorable' Boons/Banes; the text says remaining targets, which is correct.</t>
+          <t>Approved: any Main Action spell that requires a roll; 1 Bane; simultaneous vanish; return at the start of your next turn; visible free destination within 4 squares.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -2523,7 +2501,7 @@
       <c r="L10" s="8" t="inlineStr"/>
       <c r="M10" s="8" t="inlineStr"/>
     </row>
-    <row r="11" ht="66.5" customHeight="1">
+    <row r="11" ht="91.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -2541,32 +2519,32 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Up to two creatures affected by your Standard or Strong Main Action spell.</t>
+          <t>Self, when you cast a single-target spell that requires a roll.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>After the spell resolves, push each chosen creature up to 2 squares directly away from you. Choose the order. This adds no direct damage; use normal forced movement and collisions. The spell need not already cause displacement.</t>
+          <t>You take 2 Banes on defense rolls until the start of your next turn. Choose two different targets or directions before rolling. Resolve the triggering spell twice, once for each choice, with a separate roll for each casting. Each casting uses the spell’s normal range and effects. Pay any costs for the spell once.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Pushes up to two spell targets 2 squares. Useful, but a modest effect for a Master signature slot.</t>
+          <t>Self-only Reaction that splits a single-target spell into two castings with separate rolls, at the cost of 2 Banes on defense until the next turn. Strong nova with a real defensive risk.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Consider a Master-scale rider: push 3, choose direction, or knock prone on a Strong result. Otherwise accept it as a simple option and say so in the class guidance.</t>
+          <t>Approved: single-target spell with a roll; choose two different targets or directions before rolling; separate rolls; pay the spell cost once; 2 Banes on defense until the start of the next turn.</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
@@ -2582,7 +2560,7 @@
       <c r="L11" s="7" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
-    <row r="12" ht="91.5" customHeight="1">
+    <row r="12" ht="79" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>7</t>
@@ -2590,7 +2568,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Fold the Distance</t>
+          <t>Folded Aegis</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -2600,32 +2578,32 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Self and optionally one adjacent willing ally; visible free destinations within 4 squares of you.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Teleport yourself to a chosen destination. You may bring the ally to a separate free square adjacent to your destination, also within range. Both destinations must fit their occupants; no opaque barrier may separate either traveler from its destination. Neither traveler provokes, and the ally spends no action.</t>
+          <t>For 2 hours, you are wrapped in magical heavy armor. You gain physical resistance 3, fire resistance 3 and cold resistance 3. Use the highest matching resistance for each damage type, to the normal cap of 3. The armor is weightless and needs no armor training.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Teleport self and one adjacent ally up to 4 squares; excellent escape and repositioning.</t>
+          <t>Folded Aegis: once per day for 2 hours, wrap yourself in magical heavy armor with resistance 3 to physical, fire and cold. Strong defensive capstone.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Clarify line of effect and whether the ally can be moved if it is immobile or Grappled. The 'no opaque barrier' clause is good.</t>
+          <t>Approved: Main Action, self, 2 hours, once per day, resistance 3 to physical, fire and cold, highest matching resistance and normal cap 3. Weightless and needs no armor training.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -2641,7 +2619,7 @@
       <c r="L12" s="8" t="inlineStr"/>
       <c r="M12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="79" customHeight="1">
+    <row r="13" ht="41.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -2664,7 +2642,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2674,17 +2652,17 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Each recipient gains 1 Boon to defenses against spells until the start of your next turn. During that time, each recipient gains Stability 2 for the first forced movement against them, including being struck in a collision chain. Use the highest applicable Stability, maximum 3.</t>
+          <t>Each recipient gains 1 Boon to defenses against spells until the start of your next turn. During that time, each recipient gains Stability 2.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Ward for self and nearby allies: 1 Boon against spells and Stability 2 against the first forced movement. Strong protective capstone.</t>
+          <t>Ward for self and nearby allies: 1 Boon against spells and Stability 2 until the start of your next turn. Strong, simple protective capstone.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Stability grant is consumed even if a higher Stability applies (text says yes) and whether allies keep the Boon if they leave the circle.</t>
+          <t>Approved: 1 Boon against spells plus Stability 2, with no special tracking or exceptions. Reapplying replaces the previous ward.</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -2717,15 +2695,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2839,10 +2814,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -2872,13 +2847,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>0</v>
@@ -2905,16 +2880,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="D8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
@@ -3057,13 +3032,13 @@
         <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
@@ -3154,7 +3129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3235,17 +3210,17 @@
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Arcane Deflection</t>
+          <t>Choose the Edge</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-arcanist-arcane-deflection</t>
+          <t>signature-arcanist-choose-the-edge</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -3255,70 +3230,30 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>2 Boons</t>
+          <t>Master feel</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Reaction grants 2 Boons to a spell defense, above the usual 1.</t>
+          <t>2-square push on up to two targets; modest for a Master slot.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Confirm 2 is intended; compare to shared defense cards.</t>
+          <t>Consider a stronger rider or accept as a simple Master option.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="29" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Choose the Edge</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>signature-arcanist-choose-the-edge</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Master feel</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2-square push on up to two targets; modest for a Master slot.</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Consider a stronger rider or accept as a simple Master option.</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J6"/>
+  <autoFilter ref="A4:J5"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H6">
+  <conditionalFormatting sqref="H5">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>H5="Keep"</formula>
     </cfRule>
@@ -3329,15 +3264,12 @@
       <formula>H5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>H5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3361,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3376,12 +3308,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3462,30 +3393,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3509,7 +3435,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -3529,7 +3454,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3549,7 +3473,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -3569,7 +3492,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3589,7 +3511,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -3609,7 +3530,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3629,7 +3549,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -3649,7 +3568,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3669,7 +3587,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -3689,7 +3606,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3709,7 +3625,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -3729,23 +3644,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
